--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD64E47-61F3-6E40-B620-BD81A8FCFA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE6973B-9A4D-9544-A2A1-CACFC7F3AA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" activeTab="3" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" activeTab="2" xr2:uid="{B6A127EC-86E5-1348-8EA3-CDC4E3346098}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="7" r:id="rId1"/>
     <sheet name="Primary" sheetId="1" r:id="rId2"/>
     <sheet name="Ext1" sheetId="2" r:id="rId3"/>
-    <sheet name="Ext2" sheetId="8" r:id="rId4"/>
+    <sheet name="Ext2" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="133">
   <si>
     <t>SIMPLE</t>
   </si>
@@ -119,6 +119,12 @@
     <t>extension name</t>
   </si>
   <si>
+    <t>TTYPE1</t>
+  </si>
+  <si>
+    <t>TFORM1</t>
+  </si>
+  <si>
     <t>SCIENCE</t>
   </si>
   <si>
@@ -158,12 +164,45 @@
     <t>VISDA</t>
   </si>
   <si>
+    <t>ASCII table extension</t>
+  </si>
+  <si>
+    <t>length of dimension 1</t>
+  </si>
+  <si>
+    <t>length of dimension 2</t>
+  </si>
+  <si>
     <t>PCOUNT</t>
   </si>
   <si>
+    <t>number of group parameters</t>
+  </si>
+  <si>
     <t>GCOUNT</t>
   </si>
   <si>
+    <t>number of groups</t>
+  </si>
+  <si>
+    <t>TFIELDS</t>
+  </si>
+  <si>
+    <t>number of table fields</t>
+  </si>
+  <si>
+    <t>TBCOL1</t>
+  </si>
+  <si>
+    <t>TTYPE2</t>
+  </si>
+  <si>
+    <t>TFORM2</t>
+  </si>
+  <si>
+    <t>TBCOL2</t>
+  </si>
+  <si>
     <t>ROISTRTX</t>
   </si>
   <si>
@@ -176,6 +215,9 @@
     <t>ROISIZEY</t>
   </si>
   <si>
+    <t>TABLE</t>
+  </si>
+  <si>
     <t>Fixed Value</t>
   </si>
   <si>
@@ -188,6 +230,15 @@
     <t>Pandora DPC</t>
   </si>
   <si>
+    <t>ExposureStartTime_us</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>TEMP_TIME</t>
+  </si>
+  <si>
     <t>CAMERAID</t>
   </si>
   <si>
@@ -356,6 +407,9 @@
     <t xml:space="preserve">v2.12 </t>
   </si>
   <si>
+    <t xml:space="preserve">D25.17 </t>
+  </si>
+  <si>
     <t>Extension</t>
   </si>
   <si>
@@ -371,6 +425,9 @@
     <t>CompImageHDU</t>
   </si>
   <si>
+    <t>TableHDU</t>
+  </si>
+  <si>
     <t xml:space="preserve">Image extension </t>
   </si>
   <si>
@@ -381,105 +438,6 @@
   </si>
   <si>
     <t xml:space="preserve">number of groups     </t>
-  </si>
-  <si>
-    <t>PFVER</t>
-  </si>
-  <si>
-    <t>v1.0.0</t>
-  </si>
-  <si>
-    <t>pandorafits version number</t>
-  </si>
-  <si>
-    <t>Flat field applied?</t>
-  </si>
-  <si>
-    <t>FLATFILE</t>
-  </si>
-  <si>
-    <t>/path/filename</t>
-  </si>
-  <si>
-    <t>Flat field file name</t>
-  </si>
-  <si>
-    <t>Flat</t>
-  </si>
-  <si>
-    <t>non linearity</t>
-  </si>
-  <si>
-    <t>wcs</t>
-  </si>
-  <si>
-    <t>gain</t>
-  </si>
-  <si>
-    <t>dark</t>
-  </si>
-  <si>
-    <t>bias</t>
-  </si>
-  <si>
-    <t>cosmic rays</t>
-  </si>
-  <si>
-    <t>bad pixel map</t>
-  </si>
-  <si>
-    <t>background</t>
-  </si>
-  <si>
-    <t>FLAT</t>
-  </si>
-  <si>
-    <t>BADPIX</t>
-  </si>
-  <si>
-    <t>Bad pixel map applied?</t>
-  </si>
-  <si>
-    <t>BIAS</t>
-  </si>
-  <si>
-    <t>Bias subtracted?</t>
-  </si>
-  <si>
-    <t>NONLIN</t>
-  </si>
-  <si>
-    <t>Non-linearity applied?</t>
-  </si>
-  <si>
-    <t>Dark subtracted?</t>
-  </si>
-  <si>
-    <t>DARK</t>
-  </si>
-  <si>
-    <t>COSMICS</t>
-  </si>
-  <si>
-    <t>GAIN</t>
-  </si>
-  <si>
-    <t>Gain applied?</t>
-  </si>
-  <si>
-    <t>BACKGND</t>
-  </si>
-  <si>
-    <t>Background Removed?</t>
-  </si>
-  <si>
-    <t>NLFILE</t>
-  </si>
-  <si>
-    <t>Non-linearity file</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
   </si>
 </sst>
 </file>
@@ -904,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C0BA10-7BB3-C74F-A1DA-9C1D8DB3A51E}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -912,13 +870,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -926,7 +884,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3" t="b">
         <v>0</v>
@@ -934,30 +892,25 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>146</v>
+      <c r="A4" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+        <v>128</v>
+      </c>
+      <c r="C4" s="3" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -980,10 +933,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>19</v>
@@ -994,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1036,13 +989,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1056,7 +1009,7 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1064,13 +1017,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1078,13 +1031,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1092,13 +1045,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1106,27 +1059,27 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1134,13 +1087,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -1148,13 +1101,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1162,74 +1115,74 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B19">
         <v>16</v>
@@ -1238,12 +1191,12 @@
         <v>16</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B20">
         <v>16</v>
@@ -1252,91 +1205,91 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C24">
         <v>2048</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>2048</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1344,13 +1297,13 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1358,13 +1311,13 @@
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C28">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1372,13 +1325,13 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C29">
         <v>1561</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1386,55 +1339,55 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C30">
         <v>40000000</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C32">
         <v>200000</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1577,7 +1530,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83271CB-FC54-E142-86E3-37282DC63805}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -1591,10 +1544,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>19</v>
@@ -1605,13 +1558,13 @@
         <v>21</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1625,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1639,7 +1592,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1650,7 +1603,7 @@
         <v>2048</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1661,7 +1614,7 @@
         <v>2048</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1672,12 +1625,12 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1686,12 +1639,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1700,29 +1653,29 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C11">
         <v>32768</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1730,10 +1683,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -1747,7 +1700,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1755,10 +1708,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1766,10 +1719,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -1777,231 +1730,222 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C25">
         <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>2048</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>2048</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
-      </c>
-      <c r="H31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
-      </c>
-      <c r="H32" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>14</v>
       </c>
@@ -2009,13 +1953,10 @@
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
-      </c>
-      <c r="H33" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>15</v>
       </c>
@@ -2023,13 +1964,10 @@
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>16</v>
       </c>
@@ -2037,13 +1975,10 @@
         <v>1561</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
-      </c>
-      <c r="H35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>17</v>
       </c>
@@ -2051,164 +1986,40 @@
         <v>40000000</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C38">
         <v>200000</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
-      </c>
-      <c r="H38" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" t="s">
         <v>115</v>
-      </c>
-      <c r="D40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C44" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C45" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46" t="s">
-        <v>119</v>
-      </c>
-      <c r="D46" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C49" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C50" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2218,14 +2029,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B12432C-B984-0240-ACD7-BB0B52B470BA}">
-  <dimension ref="A1:D34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A53A4E1-5B55-C84C-AA1F-46326674D717}">
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -2233,27 +2043,27 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>110</v>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2261,13 +2071,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2275,371 +2085,188 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
       <c r="C5">
-        <v>2048</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
       <c r="C6">
-        <v>2048</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>113</v>
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11">
-        <v>32768</v>
+        <v>27</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
+        <v>50</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="4">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
+        <v>52</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25">
-        <v>2048</v>
-      </c>
-      <c r="D25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26">
-        <v>2048</v>
-      </c>
-      <c r="D26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29">
-        <v>11</v>
-      </c>
-      <c r="D29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30">
-        <v>1561</v>
-      </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31">
-        <v>40000000</v>
-      </c>
-      <c r="D31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33">
-        <v>200000</v>
-      </c>
-      <c r="D33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="s">
-        <v>98</v>
-      </c>
+      <c r="C16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="2"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/visda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255D35F3-3307-C546-B838-62943DB27838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6977E0-86DB-BB4F-A791-9EF524D232B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="30240" windowHeight="17300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="153">
   <si>
     <t>Extension</t>
   </si>
@@ -449,6 +449,39 @@
   </si>
   <si>
     <t>910370867</t>
+  </si>
+  <si>
+    <t>PFSOFTV</t>
+  </si>
+  <si>
+    <t>0.1.0</t>
+  </si>
+  <si>
+    <t>pandorafits software version</t>
+  </si>
+  <si>
+    <t>TARG_RA</t>
+  </si>
+  <si>
+    <t>45.46099853515625</t>
+  </si>
+  <si>
+    <t>Target right ascension [deg]</t>
+  </si>
+  <si>
+    <t>TARG_DEC</t>
+  </si>
+  <si>
+    <t>-16.594999313354492</t>
+  </si>
+  <si>
+    <t>Target declination [deg]</t>
+  </si>
+  <si>
+    <t>TARG_RLL</t>
+  </si>
+  <si>
+    <t>Commanded roll [deg]</t>
   </si>
 </sst>
 </file>
@@ -467,6 +500,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -813,6 +847,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -865,8 +904,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="71" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1295,6 +1340,50 @@
       </c>
       <c r="D36" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38">
+        <v>10.450973449999999</v>
+      </c>
+      <c r="D38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1306,6 +1395,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1467,6 +1562,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,12 +1176,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dohiemZfdmffdmZf</t>
+          <t>EGXLGFVIEFVIEFVI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:33</t>
+          <t>HDU checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:33</t>
+          <t>data unit checksum updated 2026-01-07T18:03:53</t>
         </is>
       </c>
     </row>
@@ -1274,16 +1274,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DPC Observation ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEQSTART</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>VISDAFFILevel1HDUList</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1532,12 +1568,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9i1FIf0E9f0EGf0E</t>
+          <t>9gqEHfoE9foEEfoE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:33</t>
+          <t>HDU checksum updated 2026-01-07T18:03:54</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1591,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:33</t>
+          <t>data unit checksum updated 2026-01-07T18:03:54</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1958,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZnjUfngTZngTdngT</t>
+          <t>ZpgTemgTZmgTbmgT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:33</t>
+          <t>HDU checksum updated 2026-01-07T18:03:54</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1981,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:33</t>
+          <t>data unit checksum updated 2026-01-07T18:03:54</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2352,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Z03Ii03GZ03Gf03G</t>
+          <t>Zr3Hgo2GZo2Gdo2G</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:33</t>
+          <t>HDU checksum updated 2026-01-07T18:03:54</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2375,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:33</t>
+          <t>data unit checksum updated 2026-01-07T18:03:54</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,12 +1176,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EGXLGFVIEFVIEFVI</t>
+          <t>QTX2RSW1QSW1QSW1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:53</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:53</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2454833</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1320,6 +1320,24 @@
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-01-08T19:07:58.890</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1568,12 +1586,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9gqEHfoE9foEEfoE</t>
+          <t>9goEEfnE9fnECfnE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:54</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1609,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:54</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1976,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZpgTemgTZmgTbmgT</t>
+          <t>YphTbmeTZmeTameT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:54</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1999,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:54</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2370,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zr3Hgo2GZo2Gdo2G</t>
+          <t>Zr1Hdo1GZo1Gbo1G</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:54</t>
+          <t>HDU checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2393,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:54</t>
+          <t>data unit checksum updated 2026-01-08T14:07:58</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -1176,12 +1176,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>QTX2RSW1QSW1QSW1</t>
+          <t>YX8ebX7bZX7baX7b</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>DPCSEQID</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>DPC Obseravation Sequence ID</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-01-08T19:07:58.890</t>
+          <t>2026-01-16T17:19:58.144</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1586,12 +1586,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9goEEfnE9fnECfnE</t>
+          <t>9ioGEfnE9fnECfnE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YphTbmeTZmeTameT</t>
+          <t>YohVbneTZneTaneT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zr1Hdo1GZo1Gbo1G</t>
+          <t>Z11Je01GZ01Gb01G</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:07:58</t>
+          <t>HDU checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:07:58</t>
+          <t>data unit checksum updated 2026-01-16T10:19:58</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -11,7 +11,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext3" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,21 +490,6 @@
         </is>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BinTableHDU</t>
-        </is>
-      </c>
-      <c r="C5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1176,12 +1160,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YX8ebX7bZX7baX7b</t>
+          <t>aaAfbR5daXAdaX3d</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1183,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1314,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-01-16T17:19:58.144</t>
+          <t>2026-01-16T22:40:11.448</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1586,12 +1570,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9ioGEfnE9fnECfnE</t>
+          <t>Ai3FDf1EAf1EAf1E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1593,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1960,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YohVbneTZneTaneT</t>
+          <t>ZniUiniTZniTfniT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
+          <t>HDU checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>
@@ -1999,401 +1983,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BINTABLE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BINTABLE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>binary table extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>array data type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>number of array dimensions</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of dimension 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>number of group parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TFIELDS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of table fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Z11Je01GZ01Gb01G</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:19:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:19:58</t>
+          <t>data unit checksum updated 2026-01-16T15:40:11</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext4" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +492,36 @@
         </is>
       </c>
       <c r="C4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -504,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +814,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -800,7 +832,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -818,7 +850,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -836,7 +868,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>G1299384497902599936</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -854,7 +886,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2025/12/03/2025-12-03__15-00-08_VisImg_Dark_d1024x1024x0010_b1_e000200000us.sp</t>
+          <t>2026-07-12__02-42-32.525_VisImg_G1299384497902599936_d1280x1280x0010_b1_e000200000us.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -926,7 +958,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -944,7 +976,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>384</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -980,7 +1012,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -998,7 +1030,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1070,7 +1102,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>818089246</t>
+          <t>837139385</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1088,7 +1120,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>182000000</t>
+          <t>525000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1160,12 +1192,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>aaAfbR5daXAdaX3d</t>
+          <t>3ncX5lZU3lbU3lZU</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1183,20 +1215,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.4.2</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1204,120 +1236,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TARG_RA</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Target right ascension [deg]</t>
-        </is>
-      </c>
+          <t>0.6.0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TARG_DEC</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Target declination [deg]</t>
-        </is>
-      </c>
+          <t>2.9.1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Commanded roll [deg]</t>
-        </is>
-      </c>
+          <t>VISDAFFILevel1HDUList</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DPCSEQID</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>2026-08-26T01:26:35.715</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
-        <is>
-          <t>DPC Obseravation Sequence ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SEQSTART</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2454833</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DPC Observation Sequence Start</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>PFCLASS</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>VISDAFFILevel1HDUList</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PFTIME</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-01-16T22:40:11.448</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
         <is>
           <t>Pandora DPC Processing Time</t>
         </is>
@@ -1334,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,7 +1404,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1448,7 +1418,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1570,12 +1540,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ai3FDf1EAf1EAf1E</t>
+          <t>6laA9lZ56laA6lY3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1558,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2751485292</t>
+          <t>4290961373</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1610,20 +1580,6 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PFSOFTV</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1960,12 +1916,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZniUiniTZniTfniT</t>
+          <t>mL80mJ70mJ70mJ70</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:11</t>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1934,468 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2339345775</t>
+          <t>490153783</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:11</t>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FRAME</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Time frame is JD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2gfB2Zc92dcA2Zc7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2634768335</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>second</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Exposure time unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EXPTIME</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>b9Jab9JWb9Jab9JW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2111832060</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-08-25T21:26:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -1192,12 +1192,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3ncX5lZU3lbU3lZU</t>
+          <t>2lbX5kZU2kbU2kZU</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-26T01:26:35.715</t>
+          <t>2026-09-08T18:41:35.806</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,12 +1540,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6laA9lZ56laA6lY3</t>
+          <t>7kbA9kZ37kb97kZ9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mL80mJ70mJ70mJ70</t>
+          <t>mKAopI0omI7omI7o</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2gfB2Zc92dcA2Zc7</t>
+          <t>2efA5Zd82bdA2Zd5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b9Jab9JWb9Jab9JW</t>
+          <t>b8Mae8JUb8Jab8JU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:35</t>
+          <t>HDU checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:35</t>
+          <t>data unit checksum updated 2026-09-08T14:41:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level1-ffi_visda.xlsx
@@ -1192,12 +1192,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2lbX5kZU2kbU2kZU</t>
+          <t>2nbW3kZT2kbT2kZT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-08T18:41:35.806</t>
+          <t>2026-09-09T19:46:13.504</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,12 +1540,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7kbA9kZ37kb97kZ9</t>
+          <t>6laA8kY46ka96kY9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mKAopI0omI7omI7o</t>
+          <t>lL9poI6olI6olI6o</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2efA5Zd82bdA2Zd5</t>
+          <t>1deA4Zc71dcA1Zc7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b8Mae8JUb8Jab8JU</t>
+          <t>a9Lad8IVa8Iaa8IU</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:35</t>
+          <t>HDU checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:35</t>
+          <t>data unit checksum updated 2026-09-09T15:46:13</t>
         </is>
       </c>
     </row>
